--- a/client/public/templates/PriceRight_Materials_Import_Template.xlsx
+++ b/client/public/templates/PriceRight_Materials_Import_Template.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Materials Import" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Import Data" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:A12"/>
+  <cols>
+    <col min="1" max="1" width="100.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Primary Materials Import Template</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Fill in your materials on the Import Data sheet.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Each row is one material.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Required columns: Material Name, Category, Unit, Bulk Price, Bulk Quantity.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Optional columns: Purchase Currency (defaults to base currency GHS), Supplier Type (Local or Foreign).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Currency Code must match a currency configured in PriceRight Settings (GHS, USD, EUR, etc.).</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Leave Purchase Currency blank to use the base currency (GHS).</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>After filling in the template, save as CSV (File → Save As → CSV UTF-8) and upload in the import dialog.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,55 +506,9 @@
         <v>Supplier Type</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Bottle Tray - Honey 400g</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Packaging</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Ea</v>
-      </c>
-      <c r="D2" t="str">
-        <v>GHS</v>
-      </c>
-      <c r="E2">
-        <v>25</v>
-      </c>
-      <c r="F2">
-        <v>50</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Local</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Sugar</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Ingredients</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Kg</v>
-      </c>
-      <c r="D3" t="str">
-        <v>USD</v>
-      </c>
-      <c r="E3">
-        <v>320.5</v>
-      </c>
-      <c r="F3">
-        <v>25</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Foreign</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/client/public/templates/PriceRight_Materials_Import_Template.xlsx
+++ b/client/public/templates/PriceRight_Materials_Import_Template.xlsx
@@ -398,14 +398,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A61"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Primary Materials Import Template</v>
+        <v>PriceRight — Materials Import Template</v>
       </c>
     </row>
     <row r="2">
@@ -415,72 +415,319 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Fill in your materials on the Import Data sheet.</v>
+        <v>HOW TO USE THIS TEMPLATE</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Each row is one material.</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>STEPS:</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Required columns: Material Name, Category, Unit, Bulk Price, Bulk Quantity.</v>
+        <v>1. Click the "Import Data" tab at the bottom of this file</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Optional columns: Purchase Currency (defaults to base currency GHS), Supplier Type (Local or Foreign).</v>
+        <v>2. Review the sample rows to understand the expected format</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>3. Delete the sample data rows (rows 2 and below)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Currency Code must match a currency configured in PriceRight Settings (GHS, USD, EUR, etc.).</v>
+        <v xml:space="preserve">   — Keep row 1 (the column headers) — do not delete or edit it</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Leave Purchase Currency blank to use the base currency (GHS).</v>
+        <v>4. Enter your real data starting from row 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>5. Save the file (keep the .xlsx format)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>After filling in the template, save as CSV (File → Save As → CSV UTF-8) and upload in the import dialog.</v>
+        <v>6. In PriceRight go to Materials → More → Import and select this file</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>IMPORTANT NOTES:</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>— Do not rename or delete any column headers</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>— Do not add extra columns</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>— Leave optional fields blank if not needed</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>— Currency codes must match currencies set up in PriceRight</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>COLUMN GUIDE:</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">  Material Name — Required</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">    The full name of the raw material as it will appear in PriceRight</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">    Example: Cocoa Beans (Dried)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve">  SKU — Optional</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">    Your internal stock keeping unit or product code</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">    Example: RM-001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">  Category — Required</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">    The material category. Must match a category in PriceRight</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">    or a new one will be created automatically</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">    Example: Cocoa</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">  Unit — Required</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">    Unit of measure for this material</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">    Example: Kg   L   Ea   m   g</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">  Supplier — Optional</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">    Name of the supplier for this material</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">    Example: Agro Distributors Ltd</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">  Bulk Price — Required</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">    The price paid for the bulk quantity below</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Example: 562.50</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">  Bulk Quantity — Required</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">    The quantity the bulk price applies to</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">    Example: 25  (meaning GHS 562.50 for 25 Kg)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">  Currency Code — Required</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    The currency of purchase. Must be set up in PriceRight first</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Example: GHS   USD   EUR</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">  Description — Optional</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Any additional notes about this material</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Example: Premium grade sun-dried cocoa beans</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>SAMPLE DATA:</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>The Import Data sheet contains sample rows showing the correct format.</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Delete them before importing.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A61"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I4"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="19.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,27 +735,120 @@
         <v>Material Name</v>
       </c>
       <c r="B1" t="str">
+        <v>SKU</v>
+      </c>
+      <c r="C1" t="str">
         <v>Category</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Unit</v>
       </c>
-      <c r="D1" t="str">
-        <v>Purchase Currency</v>
-      </c>
       <c r="E1" t="str">
+        <v>Supplier</v>
+      </c>
+      <c r="F1" t="str">
         <v>Bulk Price</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Bulk Quantity</v>
       </c>
-      <c r="G1" t="str">
-        <v>Supplier Type</v>
+      <c r="H1" t="str">
+        <v>Currency Code</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Cocoa Beans (Dried)</v>
+      </c>
+      <c r="B2" t="str">
+        <v>RM-001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Cocoa</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Kg</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Agro Distributors Ltd</v>
+      </c>
+      <c r="F2">
+        <v>562.5</v>
+      </c>
+      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="H2" t="str">
+        <v>GHS</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Premium grade sun-dried cocoa beans</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Palm Oil (Crude)</v>
+      </c>
+      <c r="B3" t="str">
+        <v>RM-002</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Oils &amp; Fats</v>
+      </c>
+      <c r="D3" t="str">
+        <v>L</v>
+      </c>
+      <c r="E3" t="str">
+        <v>West Africa Oils</v>
+      </c>
+      <c r="F3">
+        <v>187.5</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3" t="str">
+        <v>GHS</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Refined palm oil for food production</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Packaging Film (Roll)</v>
+      </c>
+      <c r="B4" t="str">
+        <v>RM-003</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="D4" t="str">
+        <v>m</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PackRight Ltd</v>
+      </c>
+      <c r="F4">
+        <v>850</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="str">
+        <v>GHS</v>
+      </c>
+      <c r="I4" t="str">
+        <v>100m roll of clear heat-seal packaging film</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/client/public/templates/PriceRight_Materials_Import_Template.xlsx
+++ b/client/public/templates/PriceRight_Materials_Import_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A57"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
   </cols>
@@ -595,17 +595,17 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">  Supplier — Optional</v>
+        <v xml:space="preserve">  Bulk Price — Required</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">    Name of the supplier for this material</v>
+        <v xml:space="preserve">    The price paid for the bulk quantity below</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">    Example: Agro Distributors Ltd</v>
+        <v xml:space="preserve">    Example: 562.50</v>
       </c>
     </row>
     <row r="42">
@@ -615,17 +615,17 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">  Bulk Price — Required</v>
+        <v xml:space="preserve">  Bulk Quantity — Required</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    The price paid for the bulk quantity below</v>
+        <v xml:space="preserve">    The quantity the bulk price applies to</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v xml:space="preserve">    Example: 562.50</v>
+        <v xml:space="preserve">    Example: 25  (meaning GHS 562.50 for 25 Kg)</v>
       </c>
     </row>
     <row r="46">
@@ -635,17 +635,17 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">  Bulk Quantity — Required</v>
+        <v xml:space="preserve">  Currency Code — Required</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    The quantity the bulk price applies to</v>
+        <v xml:space="preserve">    The currency of purchase. Must be set up in PriceRight first</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v xml:space="preserve">    Example: 25  (meaning GHS 562.50 for 25 Kg)</v>
+        <v xml:space="preserve">    Example: GHS   USD   EUR</v>
       </c>
     </row>
     <row r="50">
@@ -655,17 +655,17 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v xml:space="preserve">  Currency Code — Required</v>
+        <v xml:space="preserve">  Description — Optional</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v xml:space="preserve">    The currency of purchase. Must be set up in PriceRight first</v>
+        <v xml:space="preserve">    Any additional notes about this material</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v xml:space="preserve">    Example: GHS   USD   EUR</v>
+        <v xml:space="preserve">    Example: Premium grade sun-dried cocoa beans</v>
       </c>
     </row>
     <row r="54">
@@ -675,49 +675,29 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v xml:space="preserve">  Description — Optional</v>
+        <v>SAMPLE DATA:</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v xml:space="preserve">    Any additional notes about this material</v>
+        <v>The Import Data sheet contains sample rows showing the correct format.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v xml:space="preserve">    Example: Premium grade sun-dried cocoa beans</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>SAMPLE DATA:</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>The Import Data sheet contains sample rows showing the correct format.</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
         <v>Delete them before importing.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A57"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -727,7 +707,6 @@
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,18 +723,15 @@
         <v>Unit</v>
       </c>
       <c r="E1" t="str">
-        <v>Supplier</v>
+        <v>Bulk Price</v>
       </c>
       <c r="F1" t="str">
-        <v>Bulk Price</v>
+        <v>Bulk Quantity</v>
       </c>
       <c r="G1" t="str">
-        <v>Bulk Quantity</v>
+        <v>Currency Code</v>
       </c>
       <c r="H1" t="str">
-        <v>Currency Code</v>
-      </c>
-      <c r="I1" t="str">
         <v>Description</v>
       </c>
     </row>
@@ -772,19 +748,16 @@
       <c r="D2" t="str">
         <v>Kg</v>
       </c>
-      <c r="E2" t="str">
-        <v>Agro Distributors Ltd</v>
+      <c r="E2">
+        <v>562.5</v>
       </c>
       <c r="F2">
-        <v>562.5</v>
-      </c>
-      <c r="G2">
         <v>25</v>
       </c>
+      <c r="G2" t="str">
+        <v>GHS</v>
+      </c>
       <c r="H2" t="str">
-        <v>GHS</v>
-      </c>
-      <c r="I2" t="str">
         <v>Premium grade sun-dried cocoa beans</v>
       </c>
     </row>
@@ -801,19 +774,16 @@
       <c r="D3" t="str">
         <v>L</v>
       </c>
-      <c r="E3" t="str">
-        <v>West Africa Oils</v>
+      <c r="E3">
+        <v>187.5</v>
       </c>
       <c r="F3">
-        <v>187.5</v>
-      </c>
-      <c r="G3">
         <v>25</v>
       </c>
+      <c r="G3" t="str">
+        <v>GHS</v>
+      </c>
       <c r="H3" t="str">
-        <v>GHS</v>
-      </c>
-      <c r="I3" t="str">
         <v>Refined palm oil for food production</v>
       </c>
     </row>
@@ -830,25 +800,22 @@
       <c r="D4" t="str">
         <v>m</v>
       </c>
-      <c r="E4" t="str">
-        <v>PackRight Ltd</v>
+      <c r="E4">
+        <v>850</v>
       </c>
       <c r="F4">
-        <v>850</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
+      <c r="G4" t="str">
+        <v>GHS</v>
+      </c>
       <c r="H4" t="str">
-        <v>GHS</v>
-      </c>
-      <c r="I4" t="str">
         <v>100m roll of clear heat-seal packaging film</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>